--- a/data/trans_dic/P79$ninguna_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P79$ninguna_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>89,47; 93,87</t>
+          <t>88,44; 92,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,76; 92,35</t>
+          <t>86,07; 90,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,08; 92,3</t>
+          <t>87,91; 91,11</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>86,34%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,51; 95,08</t>
+          <t>84,33; 89,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84,37; 88,21</t>
+          <t>83,57; 87,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86,21; 92,37</t>
+          <t>84,72; 87,85</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>87,68%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,47; 89,52</t>
+          <t>83,66; 89,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,03; 96,68</t>
+          <t>86,2; 90,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87,49; 93,6</t>
+          <t>85,73; 89,31</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80,02; 85,34</t>
+          <t>78,1; 83,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79,94; 84,35</t>
+          <t>78,74; 83,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,75; 84,11</t>
+          <t>79,31; 82,76</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,06; 90,44</t>
+          <t>84,61; 87,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>86,01; 89,4</t>
+          <t>84,46; 86,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,36; 89,15</t>
+          <t>84,93; 86,58</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>566699</t>
+          <t>609061</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>634630</t>
+          <t>630368</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1201329</t>
+          <t>1239429</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>552570; 579756</t>
+          <t>593058; 623175</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>619572; 652021</t>
+          <t>613481; 643957</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1179018; 1221659</t>
+          <t>1216133; 1260266</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1054426</t>
+          <t>886131</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>795670</t>
+          <t>886162</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1850096</t>
+          <t>1772293</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1013831; 1114206</t>
+          <t>860649; 910026</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>778031; 813464</t>
+          <t>862474; 905313</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1805366; 1934350</t>
+          <t>1738896; 1803284</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>589201</t>
+          <t>666940</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>831286</t>
+          <t>687694</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1420487</t>
+          <t>1354635</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>565155; 606063</t>
+          <t>643146; 686057</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>804633; 873746</t>
+          <t>669008; 705111</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1383099; 1479708</t>
+          <t>1324473; 1379719</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>743564</t>
+          <t>777499</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>812735</t>
+          <t>875993</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1556298</t>
+          <t>1653492</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>718245; 765953</t>
+          <t>750500; 802582</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>790758; 834353</t>
+          <t>849009; 898072</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1523517; 1586966</t>
+          <t>1617096; 1687502</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2953890</t>
+          <t>2939631</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3074321</t>
+          <t>3080217</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6028210</t>
+          <t>6019848</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2895118; 3042585</t>
+          <t>2894495; 2985086</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3028389; 3148028</t>
+          <t>3039780; 3117324</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5945894; 6138405</t>
+          <t>5961646; 6077518</t>
         </is>
       </c>
     </row>
